--- a/tests/A02_pixell_test_plan_chequing_account.xlsx
+++ b/tests/A02_pixell_test_plan_chequing_account.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lauri\Desktop\Intermediate Software Development0315\2. Assignments\assignments\assignment_02\instructions\given_files\assignment_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c7409c97bef83d8/Desktop/School/Term 2/ISD/Assignments/Donald_Trevor_Assignment/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2873F10E-F8B1-4F89-8CDF-A98B96DD770E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{2873F10E-F8B1-4F89-8CDF-A98B96DD770E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C6C282-9E95-49F5-8B02-013BC46A4462}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="3555" windowWidth="25185" windowHeight="11415" xr2:uid="{8D9DD509-55B1-455D-8036-16809AD15960}"/>
+    <workbookView xWindow="-105" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{8D9DD509-55B1-455D-8036-16809AD15960}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -249,6 +249,57 @@
   </si>
   <si>
     <t>Attributes are set to input values (ensure to test for superclass and subclass attributes)</t>
+  </si>
+  <si>
+    <t>ChequingAccount(123, 404, 1050.50, datetime.date(2025, 9, 29), -50, 0.02)</t>
+  </si>
+  <si>
+    <t>ChequingAccount(123, 404, 1050.50, datetime.date(2025, 9, 29), "-50", 0.02)</t>
+  </si>
+  <si>
+    <t>ChequingAccount(123, 404, 1050.50, "2025, 9, 29", -50, "0.02")</t>
+  </si>
+  <si>
+    <t>ChequingAccount(123, 404, -600, datetime.date(2025, 9, 29), -100, 0.02)</t>
+  </si>
+  <si>
+    <t>ChequingAccount(123, 404, -100, datetime.date(2025, 9, 29), -100, 0.02)</t>
+  </si>
+  <si>
+    <t>account_number = 123               client_number = 404                         balance = 1050.50                            date_created: datetime.date(2025,9,29)            overdraft_limit: -50                         overdraft_rate: 0.02</t>
+  </si>
+  <si>
+    <t>overdraft_limit = "-50"</t>
+  </si>
+  <si>
+    <t>overdraft_limit = -100</t>
+  </si>
+  <si>
+    <t>overdraft_rate = "0.02"</t>
+  </si>
+  <si>
+    <t>overdraft_rate = 0.02</t>
+  </si>
+  <si>
+    <t>date_created = "2025,9,29"</t>
+  </si>
+  <si>
+    <t>date_created = datetime.date.today()</t>
+  </si>
+  <si>
+    <t>ChquingAccount.get_service_charges()</t>
+  </si>
+  <si>
+    <t>service_charges = 0.50</t>
+  </si>
+  <si>
+    <t>service_charges = 25.50</t>
+  </si>
+  <si>
+    <t>print(ChequingAccount)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Number: 123 Balance: $1,050.50                          Overdraft Limit: $-50 Overdraft Rate: 2% Account Type: Chequing   </t>
   </si>
 </sst>
 </file>
@@ -1225,9 +1276,15 @@
       <c r="D7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
@@ -1239,9 +1296,15 @@
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
@@ -1253,9 +1316,15 @@
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
@@ -1267,9 +1336,15 @@
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
@@ -1281,9 +1356,15 @@
       <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="E11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
@@ -1295,9 +1376,15 @@
       <c r="D12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
@@ -1309,9 +1396,15 @@
       <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="E13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
@@ -1323,9 +1416,15 @@
       <c r="D14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="E14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" spans="2:7" ht="31.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11">

--- a/tests/A02_pixell_test_plan_chequing_account.xlsx
+++ b/tests/A02_pixell_test_plan_chequing_account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c7409c97bef83d8/Desktop/School/Term 2/ISD/Assignments/Donald_Trevor_Assignment/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{2873F10E-F8B1-4F89-8CDF-A98B96DD770E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36C6C282-9E95-49F5-8B02-013BC46A4462}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{2873F10E-F8B1-4F89-8CDF-A98B96DD770E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75355610-77CF-40F7-B505-3853ABB4C08E}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{8D9DD509-55B1-455D-8036-16809AD15960}"/>
+    <workbookView xWindow="-14640" yWindow="-2850" windowWidth="12150" windowHeight="20745" xr2:uid="{8D9DD509-55B1-455D-8036-16809AD15960}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t xml:space="preserve">Account Number: 123 Balance: $1,050.50                          Overdraft Limit: $-50 Overdraft Rate: 2% Account Type: Chequing   </t>
+  </si>
+  <si>
+    <t>Trevor Donald</t>
   </si>
 </sst>
 </file>
@@ -806,6 +809,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1231,7 +1238,9 @@
       <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16"/>
+      <c r="C3" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="D3" s="17"/>
     </row>
     <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
